--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T11:03:32+00:00</t>
+    <t>2026-02-06T08:16:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-type.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T08:16:26+00:00</t>
+    <t>2026-02-06T09:56:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,7 +123,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>2</t>
+    <t>3</t>
   </si>
   <si>
     <t>Level</t>
@@ -151,6 +151,12 @@
   </si>
   <si>
     <t>Période scolaire</t>
+  </si>
+  <si>
+    <t>MOBILITE</t>
+  </si>
+  <si>
+    <t>Mobilité</t>
   </si>
 </sst>
 </file>
@@ -460,7 +466,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -501,6 +507,18 @@
       </c>
       <c r="D3" s="2"/>
     </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="C4" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="D4" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T09:56:58+00:00</t>
+    <t>2026-02-06T10:49:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T10:49:33+00:00</t>
+    <t>2026-02-10T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T10:00:25+00:00</t>
+    <t>2026-02-11T15:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-type.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T15:08:15+00:00</t>
+    <t>2026-02-12T14:50:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,7 +123,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>3</t>
+    <t>1</t>
   </si>
   <si>
     <t>Level</t>
@@ -138,25 +138,10 @@
     <t>Definition</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>CAUSEDECES</t>
-  </si>
-  <si>
-    <t>Cause de décès</t>
-  </si>
-  <si>
     <t>PERIODESCOL</t>
   </si>
   <si>
     <t>Période scolaire</t>
-  </si>
-  <si>
-    <t>MOBILITE</t>
-  </si>
-  <si>
-    <t>Mobilité</t>
   </si>
 </sst>
 </file>
@@ -466,7 +451,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -485,39 +470,15 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>41</v>
       </c>
-      <c r="B2" t="s" s="2">
+      <c r="C2" t="s" s="2">
         <v>42</v>
       </c>
-      <c r="C2" t="s" s="2">
-        <v>43</v>
-      </c>
       <c r="D2" s="2"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="C4" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D4" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-12T14:50:08+00:00</t>
+    <t>2026-02-16T09:17:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T09:17:35+00:00</t>
+    <t>2026-02-16T09:32:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-type.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T09:32:48+00:00</t>
+    <t>2026-02-16T14:58:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,25 +123,34 @@
     <t>Count</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
     <t>PERIODESCOL</t>
   </si>
   <si>
     <t>Période scolaire</t>
+  </si>
+  <si>
+    <t>OBSAMENAGEMENT</t>
+  </si>
+  <si>
+    <t>Observation sur l’aménagement du moyen de transport</t>
   </si>
 </sst>
 </file>
@@ -451,7 +460,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -470,15 +479,27 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
         <v>41</v>
       </c>
-      <c r="C2" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="D2" s="2"/>
+      <c r="B3" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="D3" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T14:58:48+00:00</t>
+    <t>2026-02-23T15:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>CodeSystem for the Observation types</t>
+    <t>CodeSystem pour la défintion des types d'Observation</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T15:44:46+00:00</t>
+    <t>2026-02-24T10:21:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T10:21:42+00:00</t>
+    <t>2026-02-24T16:53:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T16:53:25+00:00</t>
+    <t>2026-02-25T09:45:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T09:45:56+00:00</t>
+    <t>2026-02-26T08:21:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-type.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/CodeSystem-tddui-observation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T08:21:36+00:00</t>
+    <t>2026-02-26T10:20:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
